--- a/artfynd/A 42828-2021 artfynd.xlsx
+++ b/artfynd/A 42828-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42828-2021 artfynd.xlsx
+++ b/artfynd/A 42828-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102660998</v>
+        <v>102661013</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508454.2928739911</v>
+        <v>508454</v>
       </c>
       <c r="R2" t="n">
-        <v>6885757.246389719</v>
+        <v>6885757</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102660155</v>
+        <v>102660179</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508507.9310901754</v>
+        <v>508508</v>
       </c>
       <c r="R3" t="n">
-        <v>6885684.805582983</v>
+        <v>6885684</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -867,19 +847,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102660188</v>
+        <v>102660139</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508507.9310901754</v>
+        <v>508508</v>
       </c>
       <c r="R4" t="n">
-        <v>6885684.805582983</v>
+        <v>6885684</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -983,19 +948,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102660179</v>
+        <v>102660998</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508507.9310901754</v>
+        <v>508454</v>
       </c>
       <c r="R5" t="n">
-        <v>6885684.805582983</v>
+        <v>6885757</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,19 +1049,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102660139</v>
+        <v>102660155</v>
       </c>
       <c r="B6" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508507.9310901754</v>
+        <v>508508</v>
       </c>
       <c r="R6" t="n">
-        <v>6885684.805582983</v>
+        <v>6885684</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1215,19 +1150,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102660148</v>
+        <v>102660188</v>
       </c>
       <c r="B7" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508507.9310901754</v>
+        <v>508508</v>
       </c>
       <c r="R7" t="n">
-        <v>6885684.805582983</v>
+        <v>6885684</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1331,19 +1251,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102661013</v>
+        <v>102660146</v>
       </c>
       <c r="B8" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508454.2928739911</v>
+        <v>508508</v>
       </c>
       <c r="R8" t="n">
-        <v>6885757.246389719</v>
+        <v>6885684</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1447,19 +1352,9 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 42828-2021 artfynd.xlsx
+++ b/artfynd/A 42828-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102661013</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102660179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102660139</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102660998</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102660155</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102660188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102660146</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>